--- a/output/StructureDefinition-BRIntervaloDoses.xlsx
+++ b/output/StructureDefinition-BRIntervaloDoses.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T19:02:54-03:00</t>
+    <t>2026-09-22T22:11:28-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRIntervaloDoses.xlsx
+++ b/output/StructureDefinition-BRIntervaloDoses.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T22:11:28-03:00</t>
+    <t>2026-09-30T19:01:17-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRIntervaloDoses.xlsx
+++ b/output/StructureDefinition-BRIntervaloDoses.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T19:01:17-03:00</t>
+    <t>2026-10-08T21:31:18-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -315,6 +315,15 @@
     <t>periodUnit</t>
   </si>
   <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Define a unidade de tempo segundo o UCUM</t>
+  </si>
+  <si>
+    <t>http://www.saude.gov.br/fhir/r4/ValueSet/BRUnidadeTempo</t>
+  </si>
+  <si>
     <t>Extension.extension:periodUnit.id</t>
   </si>
   <si>
@@ -379,15 +388,6 @@
   </si>
   <si>
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Define a unidade de tempo segundo o UCUM</t>
-  </si>
-  <si>
-    <t>http://www.saude.gov.br/fhir/r4/ValueSet/BRUnidadeTempo</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -1295,13 +1295,13 @@
         <v>76</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="AA5" t="s" s="2">
         <v>76</v>
@@ -1339,10 +1339,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1442,14 +1442,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -1471,13 +1471,13 @@
         <v>91</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -1547,10 +1547,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1573,16 +1573,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1632,7 +1632,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>88</v>
@@ -1647,15 +1647,15 @@
         <v>76</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1678,13 +1678,13 @@
         <v>76</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1711,13 +1711,13 @@
         <v>76</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="AA9" t="s" s="2">
         <v>76</v>
@@ -1750,7 +1750,7 @@
         <v>123</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -1887,13 +1887,13 @@
         <v>91</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M11" t="s" s="2">
         <v>130</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2174,7 +2174,7 @@
         <v>139</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2277,11 +2277,11 @@
         <v>140</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -2303,13 +2303,13 @@
         <v>91</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2382,7 +2382,7 @@
         <v>141</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2405,16 +2405,16 @@
         <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -2464,7 +2464,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>88</v>
@@ -2479,7 +2479,7 @@
         <v>76</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17">
@@ -2487,7 +2487,7 @@
         <v>142</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2516,7 +2516,7 @@
         <v>137</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2582,15 +2582,15 @@
         <v>123</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2613,16 +2613,16 @@
         <v>76</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2672,7 +2672,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>88</v>
@@ -2687,7 +2687,7 @@
         <v>76</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19">
@@ -2721,10 +2721,10 @@
         <v>144</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2790,7 +2790,7 @@
         <v>123</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
